--- a/msm/demo/msm_tables.xlsx
+++ b/msm/demo/msm_tables.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="157" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="314" uniqueCount="148">
   <si>
     <t>Outcome Model (logistic)</t>
   </si>
@@ -369,6 +369,99 @@
   <si>
     <t>1.000</t>
   </si>
+  <si>
+    <t>0.766</t>
+  </si>
+  <si>
+    <t>(0.397, 1.478)</t>
+  </si>
+  <si>
+    <t>(0.668, 1.409)</t>
+  </si>
+  <si>
+    <t>(0.971, 1.057)</t>
+  </si>
+  <si>
+    <t>(0.478, 1.740)</t>
+  </si>
+  <si>
+    <t>(0.011, 0.037)</t>
+  </si>
+  <si>
+    <t>(0.024, 0.064)</t>
+  </si>
+  <si>
+    <t>(0.038, 0.089)</t>
+  </si>
+  <si>
+    <t>(0.054, 0.119)</t>
+  </si>
+  <si>
+    <t>(0.069, 0.165)</t>
+  </si>
+  <si>
+    <t>(0.008, 0.033)</t>
+  </si>
+  <si>
+    <t>(0.020, 0.052)</t>
+  </si>
+  <si>
+    <t>(0.033, 0.073)</t>
+  </si>
+  <si>
+    <t>(0.047, 0.098)</t>
+  </si>
+  <si>
+    <t>(0.064, 0.134)</t>
+  </si>
+  <si>
+    <t>(-0.012, 0.007)</t>
+  </si>
+  <si>
+    <t>(-0.023, 0.013)</t>
+  </si>
+  <si>
+    <t>(-0.038, 0.019)</t>
+  </si>
+  <si>
+    <t>(-0.054, 0.027)</t>
+  </si>
+  <si>
+    <t>(-0.071, 0.043)</t>
+  </si>
+  <si>
+    <t>-0.021</t>
+  </si>
+  <si>
+    <t>-99.9%</t>
+  </si>
+  <si>
+    <t>-87.9%</t>
+  </si>
+  <si>
+    <t>6.8%</t>
+  </si>
+  <si>
+    <t>0.980</t>
+  </si>
+  <si>
+    <t>0.376</t>
+  </si>
+  <si>
+    <t>0.932</t>
+  </si>
+  <si>
+    <t>2.793</t>
+  </si>
+  <si>
+    <t>3998.5</t>
+  </si>
+  <si>
+    <t>0.397 - 1.478</t>
+  </si>
+  <si>
+    <t>1.936</t>
+  </si>
 </sst>
 </file>
 
@@ -377,7 +470,7 @@
   <numFmts count="1">
     <numFmt numFmtId="166" formatCode="0.000"/>
   </numFmts>
-  <fonts count="665">
+  <fonts count="1329">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -3183,8 +3276,2809 @@
       <sz val="10"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <i/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
-  <fills count="55">
+  <fills count="108">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3456,8 +6350,273 @@
         <fgColor rgb="FFDBE5F1"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBE5F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBE5F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBE5F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBE5F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBE5F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBE5F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBE5F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBE5F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBE5F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBE5F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBE5F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBE5F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBE5F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBE5F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBE5F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBE5F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBE5F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBE5F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBE5F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBE5F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBE5F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBE5F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBE5F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBE5F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBE5F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBE5F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBE5F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBE5F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBE5F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBE5F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBE5F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBE5F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBE5F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBE5F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBE5F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBE5F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBE5F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBE5F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBE5F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBE5F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBE5F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBE5F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBE5F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBE5F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBE5F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBE5F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBE5F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBE5F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBE5F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBE5F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBE5F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBE5F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBE5F1"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="484">
+  <borders count="967">
     <border>
       <left/>
       <right/>
@@ -6696,11 +9855,3242 @@
       <bottom style="medium"/>
       <diagonal style="none"/>
     </border>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="medium"/>
+      <bottom style="medium"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="medium"/>
+      <bottom style="medium"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="medium"/>
+      <bottom style="medium"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="medium"/>
+      <bottom style="medium"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="medium"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="medium"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="medium"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="medium"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="medium"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="medium"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="medium"/>
+      <diagonal style="none"/>
+    </border>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="medium"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="medium"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="medium"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="medium"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="medium"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="medium"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="medium"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="medium"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="medium"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="medium"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="medium"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="medium"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="medium"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="medium"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="medium"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="medium"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="medium"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="medium"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="medium"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="medium"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="medium"/>
+      <diagonal style="none"/>
+    </border>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="medium"/>
+      <bottom style="medium"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="medium"/>
+      <bottom style="medium"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="medium"/>
+      <bottom style="medium"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="medium"/>
+      <bottom style="medium"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="medium"/>
+      <bottom style="medium"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="medium"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="medium"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="medium"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="medium"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="medium"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border/>
+    <border/>
+    <border/>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="medium"/>
+      <bottom style="medium"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="medium"/>
+      <bottom style="medium"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="medium"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="medium"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="medium"/>
+      <diagonal style="none"/>
+    </border>
+    <border/>
+    <border/>
+    <border/>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="medium"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="medium"/>
+      <bottom style="medium"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="medium"/>
+      <bottom style="medium"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="medium"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="medium"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="medium"/>
+      <diagonal style="none"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="484">
+  <cellXfs count="967">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0"/>
@@ -8556,6 +14946,1863 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="664" fillId="0" borderId="483" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="484" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="485" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="486" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="487" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="488" xfId="0"/>
+    <xf numFmtId="166" fontId="665" fillId="0" borderId="489" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="666" fillId="0" borderId="490" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="667" fillId="0" borderId="491" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="668" fillId="0" borderId="492" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="669" fillId="0" borderId="493" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="670" fillId="0" borderId="494" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="672" fillId="0" borderId="495" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="674" fillId="0" borderId="496" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="676" fillId="0" borderId="497" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="678" fillId="0" borderId="498" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="680" fillId="0" borderId="499" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="682" fillId="0" borderId="500" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="684" fillId="0" borderId="501" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="686" fillId="0" borderId="502" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="688" fillId="0" borderId="503" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="690" fillId="0" borderId="504" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="692" fillId="0" borderId="505" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="694" fillId="0" borderId="506" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="696" fillId="0" borderId="507" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="698" fillId="0" borderId="508" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="700" fillId="0" borderId="509" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="702" fillId="0" borderId="510" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="704" fillId="0" borderId="511" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="706" fillId="0" borderId="512" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="708" fillId="0" borderId="513" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="710" fillId="0" borderId="514" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="712" fillId="0" borderId="515" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="714" fillId="0" borderId="516" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="716" fillId="0" borderId="517" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="718" fillId="0" borderId="518" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="720" fillId="0" borderId="519" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="722" fillId="0" borderId="520" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="724" fillId="0" borderId="521" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="726" fillId="0" borderId="522" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="728" fillId="0" borderId="523" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="730" fillId="0" borderId="524" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="732" fillId="0" borderId="525" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="734" fillId="0" borderId="526" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="736" fillId="0" borderId="527" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="738" fillId="0" borderId="528" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="740" fillId="0" borderId="529" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="742" fillId="0" borderId="530" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="743" fillId="0" borderId="531" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="744" fillId="0" borderId="532" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="745" fillId="0" borderId="533" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="747" fillId="0" borderId="534" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="749" fillId="0" borderId="535" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="751" fillId="0" borderId="536" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="753" fillId="0" borderId="537" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="755" fillId="0" borderId="538" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="756" fillId="0" borderId="539" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="757" fillId="0" borderId="540" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="758" fillId="0" borderId="541" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="759" fillId="0" borderId="542" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="760" fillId="0" borderId="543" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="761" fillId="0" borderId="544" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="762" fillId="0" borderId="545" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="763" fillId="0" borderId="546" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="764" fillId="0" borderId="547" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="765" fillId="0" borderId="548" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="766" fillId="0" borderId="549" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="767" fillId="0" borderId="550" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="768" fillId="55" borderId="551" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="769" fillId="56" borderId="552" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="770" fillId="57" borderId="553" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="771" fillId="58" borderId="554" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="772" fillId="59" borderId="555" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="773" fillId="60" borderId="556" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="774" fillId="61" borderId="557" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="775" fillId="62" borderId="558" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="776" fillId="63" borderId="559" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="777" fillId="64" borderId="560" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="778" fillId="65" borderId="561" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="779" fillId="66" borderId="562" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="780" fillId="0" borderId="563" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="781" fillId="0" borderId="564" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="782" fillId="0" borderId="565" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="783" fillId="0" borderId="566" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="784" fillId="0" borderId="567" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="785" fillId="0" borderId="568" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="786" fillId="0" borderId="569" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="787" fillId="0" borderId="570" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="788" fillId="0" borderId="571" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="789" fillId="0" borderId="572" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="790" fillId="0" borderId="573" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="791" fillId="0" borderId="574" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="792" fillId="0" borderId="575" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="793" fillId="0" borderId="576" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="794" fillId="0" borderId="577" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="795" fillId="0" borderId="578" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="796" fillId="0" borderId="579" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="797" fillId="0" borderId="580" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="798" fillId="0" borderId="581" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="799" fillId="0" borderId="582" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="800" fillId="0" borderId="583" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="801" fillId="0" borderId="584" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="585" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="586" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="587" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="588" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="589" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="590" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="591" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="592" xfId="0"/>
+    <xf numFmtId="0" fontId="803" fillId="0" borderId="593" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="805" fillId="0" borderId="594" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="807" fillId="0" borderId="595" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="809" fillId="0" borderId="596" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="811" fillId="0" borderId="597" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="813" fillId="0" borderId="598" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="815" fillId="0" borderId="599" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="817" fillId="0" borderId="600" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="819" fillId="0" borderId="601" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="821" fillId="0" borderId="602" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="823" fillId="0" borderId="603" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="825" fillId="0" borderId="604" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="827" fillId="0" borderId="605" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="829" fillId="0" borderId="606" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="831" fillId="0" borderId="607" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="833" fillId="0" borderId="608" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="835" fillId="0" borderId="609" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="837" fillId="0" borderId="610" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="839" fillId="0" borderId="611" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="841" fillId="0" borderId="612" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="843" fillId="0" borderId="613" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="845" fillId="0" borderId="614" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="847" fillId="0" borderId="615" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="849" fillId="0" borderId="616" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="851" fillId="0" borderId="617" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="853" fillId="0" borderId="618" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="855" fillId="0" borderId="619" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="857" fillId="0" borderId="620" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="859" fillId="0" borderId="621" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="861" fillId="0" borderId="622" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="863" fillId="0" borderId="623" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="865" fillId="0" borderId="624" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="867" fillId="0" borderId="625" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="869" fillId="0" borderId="626" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="871" fillId="0" borderId="627" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="873" fillId="0" borderId="628" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="875" fillId="0" borderId="629" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="877" fillId="0" borderId="630" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="879" fillId="0" borderId="631" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="881" fillId="0" borderId="632" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="883" fillId="0" borderId="633" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="885" fillId="0" borderId="634" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="887" fillId="0" borderId="635" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="889" fillId="0" borderId="636" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="891" fillId="0" borderId="637" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="893" fillId="0" borderId="638" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="895" fillId="0" borderId="639" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="897" fillId="0" borderId="640" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="899" fillId="0" borderId="641" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="901" fillId="0" borderId="642" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="903" fillId="0" borderId="643" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="905" fillId="0" borderId="644" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="907" fillId="0" borderId="645" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="909" fillId="0" borderId="646" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="911" fillId="0" borderId="647" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="913" fillId="0" borderId="648" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="915" fillId="0" borderId="649" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="917" fillId="0" borderId="650" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="919" fillId="0" borderId="651" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="921" fillId="0" borderId="652" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="923" fillId="0" borderId="653" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="925" fillId="0" borderId="654" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="927" fillId="0" borderId="655" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="928" fillId="0" borderId="656" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="929" fillId="0" borderId="657" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="930" fillId="0" borderId="658" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="932" fillId="0" borderId="659" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="933" fillId="0" borderId="660" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="934" fillId="0" borderId="661" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="935" fillId="0" borderId="662" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="936" fillId="0" borderId="663" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="937" fillId="0" borderId="664" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="938" fillId="0" borderId="665" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="939" fillId="0" borderId="666" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="940" fillId="0" borderId="667" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="941" fillId="0" borderId="668" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="943" fillId="0" borderId="669" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="944" fillId="0" borderId="670" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="945" fillId="0" borderId="671" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="946" fillId="0" borderId="672" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="948" fillId="0" borderId="673" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="949" fillId="0" borderId="674" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="950" fillId="0" borderId="675" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="951" fillId="0" borderId="676" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="953" fillId="0" borderId="677" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="954" fillId="0" borderId="678" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="956" fillId="0" borderId="679" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="958" fillId="0" borderId="680" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="960" fillId="0" borderId="681" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="962" fillId="0" borderId="682" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="964" fillId="0" borderId="683" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="966" fillId="0" borderId="684" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="968" fillId="0" borderId="685" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="969" fillId="0" borderId="686" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="970" fillId="0" borderId="687" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="971" fillId="0" borderId="688" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="972" fillId="0" borderId="689" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="973" fillId="0" borderId="690" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="974" fillId="0" borderId="691" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="975" fillId="0" borderId="692" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="976" fillId="0" borderId="693" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="977" fillId="0" borderId="694" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="978" fillId="0" borderId="695" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="979" fillId="0" borderId="696" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="980" fillId="0" borderId="697" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="981" fillId="0" borderId="698" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="982" fillId="0" borderId="699" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="983" fillId="0" borderId="700" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="984" fillId="0" borderId="701" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="985" fillId="0" borderId="702" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="986" fillId="0" borderId="703" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="987" fillId="0" borderId="704" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="988" fillId="0" borderId="705" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="989" fillId="0" borderId="706" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="990" fillId="67" borderId="707" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="991" fillId="68" borderId="708" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="992" fillId="69" borderId="709" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="993" fillId="70" borderId="710" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="994" fillId="71" borderId="711" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="995" fillId="72" borderId="712" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="996" fillId="73" borderId="713" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="997" fillId="74" borderId="714" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="998" fillId="75" borderId="715" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="999" fillId="76" borderId="716" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1000" fillId="77" borderId="717" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1001" fillId="78" borderId="718" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1002" fillId="79" borderId="719" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1003" fillId="80" borderId="720" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1004" fillId="0" borderId="721" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1005" fillId="0" borderId="722" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1006" fillId="0" borderId="723" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1007" fillId="0" borderId="724" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1008" fillId="0" borderId="725" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1009" fillId="0" borderId="726" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1010" fillId="0" borderId="727" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1011" fillId="0" borderId="728" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1012" fillId="0" borderId="729" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1013" fillId="0" borderId="730" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1014" fillId="0" borderId="731" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1015" fillId="0" borderId="732" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1016" fillId="0" borderId="733" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1017" fillId="0" borderId="734" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1018" fillId="0" borderId="735" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1019" fillId="0" borderId="736" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1020" fillId="0" borderId="737" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1021" fillId="0" borderId="738" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1022" fillId="0" borderId="739" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1023" fillId="0" borderId="740" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1024" fillId="0" borderId="741" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1025" fillId="0" borderId="742" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1026" fillId="0" borderId="743" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1027" fillId="0" borderId="744" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1028" fillId="0" borderId="745" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1029" fillId="0" borderId="746" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1030" fillId="0" borderId="747" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1031" fillId="0" borderId="748" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1032" fillId="0" borderId="749" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1033" fillId="0" borderId="750" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1034" fillId="0" borderId="751" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1035" fillId="0" borderId="752" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1036" fillId="0" borderId="753" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1037" fillId="0" borderId="754" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1038" fillId="0" borderId="755" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1039" fillId="0" borderId="756" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1040" fillId="0" borderId="757" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1041" fillId="0" borderId="758" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1042" fillId="0" borderId="759" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1043" fillId="0" borderId="760" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1044" fillId="0" borderId="761" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1045" fillId="0" borderId="762" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="763" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="764" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="765" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="766" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="767" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="768" xfId="0"/>
+    <xf numFmtId="0" fontId="1047" fillId="0" borderId="769" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1049" fillId="0" borderId="770" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1051" fillId="0" borderId="771" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1053" fillId="0" borderId="772" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1055" fillId="0" borderId="773" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1057" fillId="0" borderId="774" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1059" fillId="0" borderId="775" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1061" fillId="0" borderId="776" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1063" fillId="0" borderId="777" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1065" fillId="0" borderId="778" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1067" fillId="0" borderId="779" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1069" fillId="0" borderId="780" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1071" fillId="0" borderId="781" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1073" fillId="0" borderId="782" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1075" fillId="0" borderId="783" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1077" fillId="0" borderId="784" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1079" fillId="0" borderId="785" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1081" fillId="0" borderId="786" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1083" fillId="0" borderId="787" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1085" fillId="0" borderId="788" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1087" fillId="0" borderId="789" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1089" fillId="0" borderId="790" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1091" fillId="0" borderId="791" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1093" fillId="0" borderId="792" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1095" fillId="0" borderId="793" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1097" fillId="0" borderId="794" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1099" fillId="0" borderId="795" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1101" fillId="0" borderId="796" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1103" fillId="0" borderId="797" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1105" fillId="0" borderId="798" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1107" fillId="0" borderId="799" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1109" fillId="0" borderId="800" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1111" fillId="0" borderId="801" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1113" fillId="0" borderId="802" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1115" fillId="0" borderId="803" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1117" fillId="0" borderId="804" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1119" fillId="0" borderId="805" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1121" fillId="0" borderId="806" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1123" fillId="0" borderId="807" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1125" fillId="0" borderId="808" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1126" fillId="0" borderId="809" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1127" fillId="0" borderId="810" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1128" fillId="0" borderId="811" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1130" fillId="0" borderId="812" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1132" fillId="0" borderId="813" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1134" fillId="0" borderId="814" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1136" fillId="0" borderId="815" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1138" fillId="0" borderId="816" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1140" fillId="0" borderId="817" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1141" fillId="0" borderId="818" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1142" fillId="0" borderId="819" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1143" fillId="0" borderId="820" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1144" fillId="0" borderId="821" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1145" fillId="0" borderId="822" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1146" fillId="0" borderId="823" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1147" fillId="0" borderId="824" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1148" fillId="0" borderId="825" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1149" fillId="0" borderId="826" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1150" fillId="0" borderId="827" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1151" fillId="0" borderId="828" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1152" fillId="0" borderId="829" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1153" fillId="0" borderId="830" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1154" fillId="0" borderId="831" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1155" fillId="0" borderId="832" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1156" fillId="81" borderId="833" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1157" fillId="82" borderId="834" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1158" fillId="83" borderId="835" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1159" fillId="84" borderId="836" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1160" fillId="85" borderId="837" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1161" fillId="86" borderId="838" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1162" fillId="87" borderId="839" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1163" fillId="88" borderId="840" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1164" fillId="89" borderId="841" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1165" fillId="90" borderId="842" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1166" fillId="91" borderId="843" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1167" fillId="92" borderId="844" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1168" fillId="93" borderId="845" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1169" fillId="94" borderId="846" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1170" fillId="95" borderId="847" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1171" fillId="0" borderId="848" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1172" fillId="0" borderId="849" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1173" fillId="0" borderId="850" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1174" fillId="0" borderId="851" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1175" fillId="0" borderId="852" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1176" fillId="0" borderId="853" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1177" fillId="0" borderId="854" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1178" fillId="0" borderId="855" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1179" fillId="0" borderId="856" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1180" fillId="0" borderId="857" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1181" fillId="0" borderId="858" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1182" fillId="0" borderId="859" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1183" fillId="0" borderId="860" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1184" fillId="0" borderId="861" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1185" fillId="0" borderId="862" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1186" fillId="0" borderId="863" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1187" fillId="0" borderId="864" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1188" fillId="0" borderId="865" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1189" fillId="0" borderId="866" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1190" fillId="0" borderId="867" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1191" fillId="0" borderId="868" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1193" fillId="0" borderId="869" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="870" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="871" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="872" xfId="0"/>
+    <xf numFmtId="0" fontId="1195" fillId="0" borderId="873" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1197" fillId="0" borderId="874" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1199" fillId="0" borderId="875" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1201" fillId="0" borderId="876" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1203" fillId="0" borderId="877" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1205" fillId="0" borderId="878" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1207" fillId="0" borderId="879" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1209" fillId="0" borderId="880" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1211" fillId="0" borderId="881" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1213" fillId="0" borderId="882" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1215" fillId="0" borderId="883" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1217" fillId="0" borderId="884" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1219" fillId="0" borderId="885" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1221" fillId="0" borderId="886" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1223" fillId="0" borderId="887" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1225" fillId="0" borderId="888" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1227" fillId="0" borderId="889" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1229" fillId="0" borderId="890" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1231" fillId="0" borderId="891" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1233" fillId="0" borderId="892" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1235" fillId="0" borderId="893" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1237" fillId="0" borderId="894" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1239" fillId="0" borderId="895" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1241" fillId="0" borderId="896" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1242" fillId="0" borderId="897" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1243" fillId="0" borderId="898" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1244" fillId="0" borderId="899" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1246" fillId="0" borderId="900" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1248" fillId="0" borderId="901" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1250" fillId="0" borderId="902" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1251" fillId="0" borderId="903" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1252" fillId="0" borderId="904" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1253" fillId="0" borderId="905" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1254" fillId="0" borderId="906" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1255" fillId="0" borderId="907" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1256" fillId="0" borderId="908" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1257" fillId="96" borderId="909" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1258" fillId="97" borderId="910" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1259" fillId="98" borderId="911" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1260" fillId="99" borderId="912" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1261" fillId="100" borderId="913" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1262" fillId="101" borderId="914" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1263" fillId="0" borderId="915" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1264" fillId="0" borderId="916" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1265" fillId="0" borderId="917" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1266" fillId="0" borderId="918" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1267" fillId="0" borderId="919" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1268" fillId="0" borderId="920" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1269" fillId="0" borderId="921" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1270" fillId="0" borderId="922" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1271" fillId="0" borderId="923" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1272" fillId="0" borderId="924" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1273" fillId="0" borderId="925" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="926" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="927" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="928" xfId="0"/>
+    <xf numFmtId="0" fontId="1275" fillId="0" borderId="929" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1277" fillId="0" borderId="930" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1279" fillId="0" borderId="931" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1281" fillId="0" borderId="932" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1283" fillId="0" borderId="933" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1285" fillId="0" borderId="934" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1287" fillId="0" borderId="935" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1289" fillId="0" borderId="936" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1291" fillId="0" borderId="937" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1293" fillId="0" borderId="938" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1295" fillId="0" borderId="939" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1297" fillId="0" borderId="940" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1299" fillId="0" borderId="941" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1301" fillId="0" borderId="942" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1302" fillId="0" borderId="943" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1303" fillId="0" borderId="944" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1304" fillId="0" borderId="945" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1306" fillId="0" borderId="946" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1308" fillId="0" borderId="947" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1310" fillId="0" borderId="948" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1311" fillId="0" borderId="949" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1312" fillId="0" borderId="950" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1313" fillId="0" borderId="951" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1314" fillId="0" borderId="952" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1315" fillId="0" borderId="953" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1316" fillId="0" borderId="954" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1317" fillId="102" borderId="955" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1318" fillId="103" borderId="956" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1319" fillId="104" borderId="957" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1320" fillId="105" borderId="958" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1321" fillId="106" borderId="959" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1322" fillId="107" borderId="960" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1323" fillId="0" borderId="961" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1324" fillId="0" borderId="962" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1325" fillId="0" borderId="963" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1326" fillId="0" borderId="964" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1327" fillId="0" borderId="965" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1328" fillId="0" borderId="966" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -8571,121 +16818,121 @@
   <dimension ref="A1:D8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="22.7109375" style="2" customWidth="true"/>
-    <col min="2" max="2" width="10.7109375" style="3" customWidth="true"/>
-    <col min="3" max="3" width="18.7109375" style="4" customWidth="true"/>
-    <col min="4" max="4" width="10.7109375" style="5" customWidth="true"/>
+    <col min="1" max="1" width="22.7109375" style="485" customWidth="true"/>
+    <col min="2" max="2" width="10.7109375" style="486" customWidth="true"/>
+    <col min="3" max="3" width="18.7109375" style="487" customWidth="true"/>
+    <col min="4" max="4" width="10.7109375" style="488" customWidth="true"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="51" t="s">
+    <row r="1" s="484" customFormat="true" ht="30" customHeight="true">
+      <c r="A1" s="534" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="44" t="s">
+      <c r="B1" s="527" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="44" t="s">
+      <c r="C1" s="527" t="s">
         <v>8</v>
       </c>
-      <c r="D1" s="44" t="s">
+      <c r="D1" s="527" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="76" t="s">
+      <c r="A2" s="559" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="77" t="s">
+      <c r="B2" s="560" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="78" t="s">
+      <c r="C2" s="561" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="79" t="s">
+      <c r="D2" s="562" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="503" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="84">
-        <v>0.7672943522249035</v>
+      <c r="B3" s="567">
+        <v>0.76626792133636756</v>
       </c>
-      <c r="C3" s="85" t="s">
-        <v>17</v>
+      <c r="C3" s="568" t="s">
+        <v>118</v>
       </c>
-      <c r="D3" s="96" t="s">
+      <c r="D3" s="579" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="24" t="s">
+      <c r="A4" s="507" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="86">
-        <v>0.96990480543369195</v>
+      <c r="B4" s="569">
+        <v>0.97038766823310219</v>
       </c>
-      <c r="C4" s="87" t="s">
-        <v>18</v>
+      <c r="C4" s="570" t="s">
+        <v>119</v>
       </c>
-      <c r="D4" s="97" t="s">
+      <c r="D4" s="580" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="28" t="s">
+      <c r="A5" s="511" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="88">
-        <v>1.0135738905506451</v>
+      <c r="B5" s="571">
+        <v>1.01353939720834</v>
       </c>
-      <c r="C5" s="89" t="s">
-        <v>19</v>
+      <c r="C5" s="572" t="s">
+        <v>120</v>
       </c>
-      <c r="D5" s="98" t="s">
+      <c r="D5" s="581" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="32" t="s">
+      <c r="A6" s="515" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="90">
-        <v>1.052812145678234</v>
+      <c r="B6" s="573">
+        <v>1.052927408786541</v>
       </c>
-      <c r="C6" s="91" t="s">
+      <c r="C6" s="574" t="s">
         <v>20</v>
       </c>
-      <c r="D6" s="99" t="s">
+      <c r="D6" s="582" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="36" t="s">
+      <c r="A7" s="519" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="92">
-        <v>0.91156457885765974</v>
+      <c r="B7" s="575">
+        <v>0.91210781960720699</v>
       </c>
-      <c r="C7" s="93" t="s">
-        <v>21</v>
+      <c r="C7" s="576" t="s">
+        <v>121</v>
       </c>
-      <c r="D7" s="100" t="s">
+      <c r="D7" s="583" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="80" t="s">
+      <c r="A8" s="563" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="94">
-        <v>0.00049674249516860002</v>
+      <c r="B8" s="577">
+        <v>0.00049307646708570004</v>
       </c>
-      <c r="C8" s="95" t="s">
+      <c r="C8" s="578" t="s">
         <v>22</v>
       </c>
-      <c r="D8" s="101" t="s">
+      <c r="D8" s="584" t="s">
         <v>29</v>
       </c>
     </row>
@@ -8701,197 +16948,197 @@
   <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="30.7109375" style="103" customWidth="true"/>
-    <col min="2" max="2" width="12.7109375" style="104" customWidth="true"/>
-    <col min="3" max="3" width="18.7109375" style="105" customWidth="true"/>
-    <col min="4" max="4" width="12.7109375" style="106" customWidth="true"/>
-    <col min="5" max="5" width="18.7109375" style="107" customWidth="true"/>
-    <col min="6" max="6" width="13.7109375" style="108" customWidth="true"/>
-    <col min="7" max="7" width="18.7109375" style="109" customWidth="true"/>
+    <col min="1" max="1" width="30.7109375" style="586" customWidth="true"/>
+    <col min="2" max="2" width="12.7109375" style="587" customWidth="true"/>
+    <col min="3" max="3" width="18.7109375" style="588" customWidth="true"/>
+    <col min="4" max="4" width="12.7109375" style="589" customWidth="true"/>
+    <col min="5" max="5" width="18.7109375" style="590" customWidth="true"/>
+    <col min="6" max="6" width="13.7109375" style="591" customWidth="true"/>
+    <col min="7" max="7" width="18.7109375" style="592" customWidth="true"/>
   </cols>
   <sheetData>
-    <row r="1" s="102" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="176" t="s">
+    <row r="1" s="585" customFormat="true" ht="30" customHeight="true">
+      <c r="A1" s="659" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="166" t="s">
+      <c r="B1" s="649" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="166" t="s">
+      <c r="C1" s="649" t="s">
         <v>8</v>
       </c>
-      <c r="D1" s="166" t="s">
+      <c r="D1" s="649" t="s">
         <v>8</v>
       </c>
-      <c r="E1" s="166" t="s">
+      <c r="E1" s="649" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="166" t="s">
+      <c r="F1" s="649" t="s">
         <v>8</v>
       </c>
-      <c r="G1" s="166" t="s">
+      <c r="G1" s="649" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="177" t="s">
+      <c r="A2" s="660" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="187" t="s">
+      <c r="B2" s="670" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="178" t="s">
+      <c r="C2" s="661" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="191" t="s">
+      <c r="D2" s="674" t="s">
         <v>48</v>
       </c>
-      <c r="E2" s="180" t="s">
+      <c r="E2" s="663" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="195" t="s">
+      <c r="F2" s="678" t="s">
         <v>59</v>
       </c>
-      <c r="G2" s="182" t="s">
+      <c r="G2" s="665" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="231" t="s">
+      <c r="A3" s="714" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="232" t="s">
+      <c r="B3" s="715" t="s">
         <v>37</v>
       </c>
-      <c r="C3" s="233" t="s">
+      <c r="C3" s="716" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="234" t="s">
+      <c r="D3" s="717" t="s">
         <v>37</v>
       </c>
-      <c r="E3" s="235" t="s">
+      <c r="E3" s="718" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="236" t="s">
+      <c r="F3" s="719" t="s">
         <v>37</v>
       </c>
-      <c r="G3" s="237" t="s">
+      <c r="G3" s="720" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="245">
+      <c r="A4" s="728">
         <v>1</v>
       </c>
-      <c r="B4" s="246">
+      <c r="B4" s="729">
         <v>0.017999999999999999</v>
       </c>
-      <c r="C4" s="247" t="s">
-        <v>43</v>
+      <c r="C4" s="730" t="s">
+        <v>122</v>
       </c>
-      <c r="D4" s="248">
+      <c r="D4" s="731">
         <v>0.014</v>
       </c>
-      <c r="E4" s="249" t="s">
-        <v>54</v>
+      <c r="E4" s="732" t="s">
+        <v>127</v>
       </c>
-      <c r="F4" s="250">
+      <c r="F4" s="733">
         <v>-0.0040000000000000001</v>
       </c>
-      <c r="G4" s="251" t="s">
-        <v>65</v>
+      <c r="G4" s="734" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="252">
+      <c r="A5" s="735">
         <v>3</v>
       </c>
-      <c r="B5" s="253">
+      <c r="B5" s="736">
         <v>0.036999999999999998</v>
       </c>
-      <c r="C5" s="254" t="s">
-        <v>44</v>
+      <c r="C5" s="737" t="s">
+        <v>123</v>
       </c>
-      <c r="D5" s="255">
+      <c r="D5" s="738">
         <v>0.028000000000000001</v>
       </c>
-      <c r="E5" s="256" t="s">
-        <v>55</v>
+      <c r="E5" s="739" t="s">
+        <v>128</v>
       </c>
-      <c r="F5" s="257">
+      <c r="F5" s="740">
         <v>-0.0080000000000000002</v>
       </c>
-      <c r="G5" s="258" t="s">
-        <v>66</v>
+      <c r="G5" s="741" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="259">
+      <c r="A6" s="742">
         <v>5</v>
       </c>
-      <c r="B6" s="260">
+      <c r="B6" s="743">
         <v>0.057000000000000002</v>
       </c>
-      <c r="C6" s="261" t="s">
-        <v>45</v>
+      <c r="C6" s="744" t="s">
+        <v>124</v>
       </c>
-      <c r="D6" s="262">
+      <c r="D6" s="745">
         <v>0.043999999999999997</v>
       </c>
-      <c r="E6" s="263" t="s">
-        <v>56</v>
+      <c r="E6" s="746" t="s">
+        <v>129</v>
       </c>
-      <c r="F6" s="264">
+      <c r="F6" s="747">
         <v>-0.012999999999999999</v>
       </c>
-      <c r="G6" s="265" t="s">
-        <v>67</v>
+      <c r="G6" s="748" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="266">
+      <c r="A7" s="749">
         <v>7</v>
       </c>
-      <c r="B7" s="267">
+      <c r="B7" s="750">
         <v>0.082000000000000003</v>
       </c>
-      <c r="C7" s="268" t="s">
-        <v>46</v>
+      <c r="C7" s="751" t="s">
+        <v>125</v>
       </c>
-      <c r="D7" s="269">
+      <c r="D7" s="752">
         <v>0.064000000000000001</v>
       </c>
-      <c r="E7" s="270" t="s">
-        <v>57</v>
+      <c r="E7" s="753" t="s">
+        <v>130</v>
       </c>
-      <c r="F7" s="271">
+      <c r="F7" s="754">
         <v>-0.017999999999999999</v>
       </c>
-      <c r="G7" s="272" t="s">
-        <v>68</v>
+      <c r="G7" s="755" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="273">
+      <c r="A8" s="756">
         <v>9</v>
       </c>
-      <c r="B8" s="274">
+      <c r="B8" s="757">
         <v>0.11600000000000001</v>
       </c>
-      <c r="C8" s="275" t="s">
-        <v>47</v>
+      <c r="C8" s="758" t="s">
+        <v>126</v>
       </c>
-      <c r="D8" s="276">
+      <c r="D8" s="759">
         <v>0.090999999999999998</v>
       </c>
-      <c r="E8" s="277" t="s">
-        <v>58</v>
+      <c r="E8" s="760" t="s">
+        <v>131</v>
       </c>
-      <c r="F8" s="278">
+      <c r="F8" s="761">
         <v>-0.025000000000000001</v>
       </c>
-      <c r="G8" s="279" t="s">
-        <v>69</v>
+      <c r="G8" s="762" t="s">
+        <v>136</v>
       </c>
     </row>
   </sheetData>
@@ -8909,129 +17156,129 @@
   <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="43.7109375" style="281" customWidth="true"/>
-    <col min="2" max="2" width="12.7109375" style="282" customWidth="true"/>
-    <col min="3" max="3" width="12.7109375" style="283" customWidth="true"/>
-    <col min="4" max="4" width="12.7109375" style="284" customWidth="true"/>
-    <col min="5" max="5" width="12.7109375" style="285" customWidth="true"/>
+    <col min="1" max="1" width="43.7109375" style="764" customWidth="true"/>
+    <col min="2" max="2" width="12.7109375" style="765" customWidth="true"/>
+    <col min="3" max="3" width="12.7109375" style="766" customWidth="true"/>
+    <col min="4" max="4" width="12.7109375" style="767" customWidth="true"/>
+    <col min="5" max="5" width="12.7109375" style="768" customWidth="true"/>
   </cols>
   <sheetData>
-    <row r="1" s="280" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="329" t="s">
+    <row r="1" s="763" customFormat="true" ht="30" customHeight="true">
+      <c r="A1" s="812" t="s">
         <v>70</v>
       </c>
-      <c r="B1" s="321" t="s">
+      <c r="B1" s="804" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="321" t="s">
+      <c r="C1" s="804" t="s">
         <v>8</v>
       </c>
-      <c r="D1" s="321" t="s">
+      <c r="D1" s="804" t="s">
         <v>8</v>
       </c>
-      <c r="E1" s="321" t="s">
+      <c r="E1" s="804" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="360" t="s">
+      <c r="A2" s="843" t="s">
         <v>71</v>
       </c>
-      <c r="B2" s="361" t="s">
+      <c r="B2" s="844" t="s">
         <v>75</v>
       </c>
-      <c r="C2" s="362" t="s">
+      <c r="C2" s="845" t="s">
         <v>80</v>
       </c>
-      <c r="D2" s="363" t="s">
+      <c r="D2" s="846" t="s">
         <v>83</v>
       </c>
-      <c r="E2" s="364" t="s">
+      <c r="E2" s="847" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="296" t="s">
+      <c r="A3" s="779" t="s">
         <v>72</v>
       </c>
-      <c r="B3" s="365">
+      <c r="B3" s="848">
         <v>0.39500000000000002</v>
       </c>
-      <c r="C3" s="366">
-        <v>0.001</v>
+      <c r="C3" s="849">
+        <v>0</v>
       </c>
-      <c r="D3" s="367" t="s">
-        <v>84</v>
+      <c r="D3" s="850" t="s">
+        <v>138</v>
       </c>
-      <c r="E3" s="368" t="s">
+      <c r="E3" s="851" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="301" t="s">
+      <c r="A4" s="784" t="s">
         <v>73</v>
       </c>
-      <c r="B4" s="369">
+      <c r="B4" s="852">
         <v>0.17100000000000001</v>
       </c>
-      <c r="C4" s="370">
-        <v>-0.02</v>
+      <c r="C4" s="853">
+        <v>-0.021000000000000001</v>
       </c>
-      <c r="D4" s="371" t="s">
-        <v>85</v>
+      <c r="D4" s="854" t="s">
+        <v>139</v>
       </c>
-      <c r="E4" s="372" t="s">
+      <c r="E4" s="855" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="306" t="s">
+      <c r="A5" s="789" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="373">
+      <c r="B5" s="856">
         <v>0.128</v>
       </c>
-      <c r="C5" s="374">
+      <c r="C5" s="857">
         <v>0.13700000000000001</v>
       </c>
-      <c r="D5" s="375" t="s">
-        <v>86</v>
+      <c r="D5" s="858" t="s">
+        <v>140</v>
       </c>
-      <c r="E5" s="376" t="s">
+      <c r="E5" s="859" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="381" t="s">
+      <c r="A6" s="864" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="382">
+      <c r="B6" s="865">
         <v>0.115</v>
       </c>
-      <c r="C6" s="383">
+      <c r="C6" s="866">
         <v>0.11600000000000001</v>
       </c>
-      <c r="D6" s="384" t="s">
+      <c r="D6" s="867" t="s">
         <v>87</v>
       </c>
-      <c r="E6" s="385" t="s">
+      <c r="E6" s="868" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="386" t="s">
+      <c r="A7" s="869" t="s">
         <v>74</v>
       </c>
-      <c r="B7" s="316" t="s">
+      <c r="B7" s="799" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="316" t="s">
+      <c r="C7" s="799" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="316" t="s">
+      <c r="D7" s="799" t="s">
         <v>8</v>
       </c>
-      <c r="E7" s="316" t="s">
+      <c r="E7" s="799" t="s">
         <v>8</v>
       </c>
     </row>
@@ -9048,95 +17295,95 @@
   <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" style="388" customWidth="true"/>
-    <col min="2" max="2" width="12.7109375" style="389" customWidth="true"/>
+    <col min="1" max="1" width="18.7109375" style="871" customWidth="true"/>
+    <col min="2" max="2" width="12.7109375" style="872" customWidth="true"/>
   </cols>
   <sheetData>
-    <row r="1" s="387" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="417" t="s">
+    <row r="1" s="870" customFormat="true" ht="30" customHeight="true">
+      <c r="A1" s="900" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="412" t="s">
+      <c r="B1" s="895" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="430" t="s">
+      <c r="A2" s="913" t="s">
         <v>91</v>
       </c>
-      <c r="B2" s="431" t="s">
+      <c r="B2" s="914" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="394" t="s">
+      <c r="A3" s="877" t="s">
         <v>92</v>
       </c>
-      <c r="B3" s="434">
-        <v>0.98499999999999999</v>
+      <c r="B3" s="917">
+        <v>0.97999999999999998</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="396" t="s">
+      <c r="A4" s="879" t="s">
         <v>93</v>
       </c>
-      <c r="B4" s="435">
-        <v>0.377</v>
+      <c r="B4" s="918">
+        <v>0.376</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="398" t="s">
+      <c r="A5" s="881" t="s">
         <v>94</v>
       </c>
-      <c r="B5" s="436">
+      <c r="B5" s="919">
         <v>0.35499999999999998</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="400" t="s">
+      <c r="A6" s="883" t="s">
         <v>95</v>
       </c>
-      <c r="B6" s="437">
+      <c r="B6" s="920">
         <v>0.35499999999999998</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="402" t="s">
+      <c r="A7" s="885" t="s">
         <v>96</v>
       </c>
-      <c r="B7" s="438">
-        <v>0.93600000000000005</v>
+      <c r="B7" s="921">
+        <v>0.93200000000000005</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="404" t="s">
+      <c r="A8" s="887" t="s">
         <v>97</v>
       </c>
-      <c r="B8" s="439">
-        <v>2.7879999999999998</v>
+      <c r="B8" s="922">
+        <v>2.7930000000000001</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="406" t="s">
+      <c r="A9" s="889" t="s">
         <v>98</v>
       </c>
-      <c r="B9" s="440">
-        <v>2.7879999999999998</v>
+      <c r="B9" s="923">
+        <v>2.7930000000000001</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="408" t="s">
+      <c r="A10" s="891" t="s">
         <v>99</v>
       </c>
-      <c r="B10" s="441">
-        <v>4001.0999999999999</v>
+      <c r="B10" s="924">
+        <v>3998.5</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="432" t="s">
+      <c r="A11" s="915" t="s">
         <v>100</v>
       </c>
-      <c r="B11" s="442" t="s">
+      <c r="B11" s="925" t="s">
         <v>108</v>
       </c>
     </row>
@@ -9152,55 +17399,55 @@
   <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="22.7109375" style="444" customWidth="true"/>
-    <col min="2" max="2" width="14.7109375" style="445" customWidth="true"/>
+    <col min="1" max="1" width="22.7109375" style="927" customWidth="true"/>
+    <col min="2" max="2" width="14.7109375" style="928" customWidth="true"/>
   </cols>
   <sheetData>
-    <row r="1" s="443" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="463" t="s">
+    <row r="1" s="926" customFormat="true" ht="30" customHeight="true">
+      <c r="A1" s="946" t="s">
         <v>109</v>
       </c>
-      <c r="B1" s="458" t="s">
+      <c r="B1" s="941" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="476" t="s">
+      <c r="A2" s="959" t="s">
         <v>110</v>
       </c>
-      <c r="B2" s="477" t="s">
+      <c r="B2" s="960" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="450" t="s">
+      <c r="A3" s="933" t="s">
         <v>111</v>
       </c>
-      <c r="B3" s="480">
-        <v>0.76700000000000002</v>
+      <c r="B3" s="963">
+        <v>0.76600000000000001</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="452" t="s">
+      <c r="A4" s="935" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="481" t="s">
-        <v>114</v>
+      <c r="B4" s="964" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="454" t="s">
+      <c r="A5" s="937" t="s">
         <v>112</v>
       </c>
-      <c r="B5" s="482">
-        <v>1.9319999999999999</v>
+      <c r="B5" s="965">
+        <v>1.9359999999999999</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="478" t="s">
+      <c r="A6" s="961" t="s">
         <v>113</v>
       </c>
-      <c r="B6" s="483">
+      <c r="B6" s="966">
         <v>1</v>
       </c>
     </row>
